--- a/appointment_forms/049_job_interview_appointment_checklist_form_template--appointment_forms.xlsx
+++ b/appointment_forms/049_job_interview_appointment_checklist_form_template--appointment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -793,7 +793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1081,12 +1081,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>cyber_security</t>
+          <t>devops</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cyber Security</t>
+          <t>DevOps</t>
         </is>
       </c>
     </row>
@@ -1098,12 +1098,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>devops</t>
+          <t>network_development</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>DevOps</t>
+          <t>Network Development</t>
         </is>
       </c>
     </row>
@@ -1115,63 +1115,63 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>network_development</t>
+          <t>data_analysis</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Network Development</t>
+          <t>Data Analysis</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>candidate_skills_choices</t>
+          <t>job_type_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>artificial_intelligence</t>
+          <t>full-time</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Full-time</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>candidate_skills_choices</t>
+          <t>job_type_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>mobile_development</t>
+          <t>part-time</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Mobile Development</t>
+          <t>Part-time</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>candidate_skills_choices</t>
+          <t>job_type_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>data_analysis</t>
+          <t>intern</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Data Analysis</t>
+          <t>Intern</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>full-time</t>
+          <t>contract</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Contract</t>
         </is>
       </c>
     </row>
@@ -1200,61 +1200,10 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>part-time</t>
+          <t>freelance</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
-        <is>
-          <t>Part-time</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>job_type_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>intern</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Intern</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>job_type_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>contract</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Contract</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>job_type_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>freelance</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
         <is>
           <t>Freelance</t>
         </is>
